--- a/artfynd/A 37568-2025 artfynd.xlsx
+++ b/artfynd/A 37568-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127383926</v>
       </c>
       <c r="B2" t="n">
-        <v>80117</v>
+        <v>80121</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>127383966</v>
       </c>
       <c r="B3" t="n">
-        <v>80117</v>
+        <v>80121</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -880,7 +880,7 @@
         <v>127383914</v>
       </c>
       <c r="B4" t="n">
-        <v>80117</v>
+        <v>80121</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 37568-2025 artfynd.xlsx
+++ b/artfynd/A 37568-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127383926</v>
       </c>
       <c r="B2" t="n">
-        <v>80121</v>
+        <v>80123</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>127383966</v>
       </c>
       <c r="B3" t="n">
-        <v>80121</v>
+        <v>80123</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -880,7 +880,7 @@
         <v>127383914</v>
       </c>
       <c r="B4" t="n">
-        <v>80121</v>
+        <v>80123</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 37568-2025 artfynd.xlsx
+++ b/artfynd/A 37568-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127383926</v>
       </c>
       <c r="B2" t="n">
-        <v>80123</v>
+        <v>80126</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>127383966</v>
       </c>
       <c r="B3" t="n">
-        <v>80123</v>
+        <v>80126</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -880,7 +880,7 @@
         <v>127383914</v>
       </c>
       <c r="B4" t="n">
-        <v>80123</v>
+        <v>80126</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 37568-2025 artfynd.xlsx
+++ b/artfynd/A 37568-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127383926</v>
       </c>
       <c r="B2" t="n">
-        <v>80126</v>
+        <v>80132</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>127383966</v>
       </c>
       <c r="B3" t="n">
-        <v>80126</v>
+        <v>80132</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -880,7 +880,7 @@
         <v>127383914</v>
       </c>
       <c r="B4" t="n">
-        <v>80126</v>
+        <v>80132</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 37568-2025 artfynd.xlsx
+++ b/artfynd/A 37568-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>127383926</v>
+        <v>127383914</v>
       </c>
       <c r="B2" t="n">
-        <v>80132</v>
+        <v>80432</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -713,10 +713,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>613139</v>
+        <v>613093</v>
       </c>
       <c r="R2" t="n">
-        <v>7118623</v>
+        <v>7118581</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -776,10 +776,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127383966</v>
+        <v>127383926</v>
       </c>
       <c r="B3" t="n">
-        <v>80132</v>
+        <v>80432</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -814,10 +814,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>613005</v>
+        <v>613139</v>
       </c>
       <c r="R3" t="n">
-        <v>7118829</v>
+        <v>7118623</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -877,10 +877,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127383914</v>
+        <v>127383966</v>
       </c>
       <c r="B4" t="n">
-        <v>80132</v>
+        <v>80432</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -915,10 +915,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>613093</v>
+        <v>613005</v>
       </c>
       <c r="R4" t="n">
-        <v>7118581</v>
+        <v>7118829</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
